--- a/experiments/results/cabp/iteration-bfs-reverse/cabp-sat-iteration-bfs-reverse.xlsx
+++ b/experiments/results/cabp/iteration-bfs-reverse/cabp-sat-iteration-bfs-reverse.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ite_cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ite_cabp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ite_cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ite_cabp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ite_cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ite_cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ite_cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.5_no_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.75_no_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,72 +435,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -546,12 +558,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -612,12 +624,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -678,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -744,12 +756,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -810,12 +822,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -876,12 +888,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -942,12 +954,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1008,12 +1020,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1074,12 +1086,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>494</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1127,28 +1139,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>237.3</t>
+          <t>195.8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1805397</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1202,12 +1218,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>249.9</t>
+          <t>273.6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>793</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1268,12 +1284,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>237.4</t>
+          <t>218.9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>856</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1334,12 +1350,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6180.3</t>
+          <t>6414.9</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1811961</t>
+          <t>1814340</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1396,12 +1412,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6207.4</t>
+          <t>6510.4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1811993</t>
+          <t>1813932</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1458,12 +1474,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4251.6</t>
+          <t>4218.2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1511,7 +1527,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>181</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1524,15 +1540,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4996.4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1807622</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>1220383</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1586,12 +1606,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5158.4</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1672,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8539.4</t>
+          <t>8369.8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>349408</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1705,25 +1725,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>259</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7660.7</t>
+          <t>7054.2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1116595</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1776,23 +1796,27 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>9192.3</t>
+          <t>7769.8</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1810621</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>72818</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1846,12 +1870,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9414.1</t>
+          <t>9248.9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>119635</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1899,28 +1923,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="K23" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11970.9</t>
+          <t>11504.5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1811465</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>38576</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1974,12 +2002,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10291.4</t>
+          <t>9842.3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>143847</t>
+          <t>66516</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2040,12 +2068,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13736.3</t>
+          <t>11264.2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>281598</t>
+          <t>116025</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2069,72 +2097,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2192,12 +2220,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2258,12 +2286,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2324,12 +2352,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2390,12 +2418,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2456,12 +2484,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2522,12 +2550,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2588,12 +2616,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2654,12 +2682,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2720,12 +2748,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>520</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2773,32 +2801,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>195.8</t>
+          <t>237.3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1805397</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2852,12 +2876,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>273.6</t>
+          <t>249.9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>613</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2918,12 +2942,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>218.9</t>
+          <t>237.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>654</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2984,12 +3008,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6414.9</t>
+          <t>6180.3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1814340</t>
+          <t>1811961</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3046,12 +3070,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6510.4</t>
+          <t>6207.4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1813932</t>
+          <t>1811993</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3108,12 +3132,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4218.2</t>
+          <t>4251.6</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3161,7 +3185,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3174,19 +3198,15 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4996.4</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1220383</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1807622</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3240,12 +3260,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5158.4</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>42973</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3306,12 +3326,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8369.8</t>
+          <t>8539.4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>303750</t>
+          <t>349408</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3359,25 +3379,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>267</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7054.2</t>
+          <t>7660.7</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>1116595</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3430,27 +3450,23 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7769.8</t>
+          <t>9192.3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>72818</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1810621</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3504,12 +3520,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9248.9</t>
+          <t>9414.1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>119635</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3557,32 +3573,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>335</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11504.5</t>
+          <t>11970.9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>38576</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811465</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3636,12 +3648,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>9842.3</t>
+          <t>10291.4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>66516</t>
+          <t>143847</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3702,12 +3714,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11264.2</t>
+          <t>13736.3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>116025</t>
+          <t>281598</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3731,72 +3743,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3841,25 +3853,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>69</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -3920,12 +3932,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3986,12 +3998,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -4052,12 +4064,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>239</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -4118,12 +4130,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -4184,12 +4196,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>255</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -4250,12 +4262,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>262</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -4316,12 +4328,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -4382,12 +4394,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>196.2</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>69926</t>
+          <t>894</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -4435,28 +4447,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K11" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>460.9</t>
+          <t>275.3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1806819</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4497,25 +4513,25 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>400.8</t>
+          <t>408.7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>39413</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -4576,12 +4592,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>432.9</t>
+          <t>310.1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -4634,20 +4650,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>288</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9496.1</t>
+          <t>9687.6</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1812365</t>
+          <t>1813421</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -4696,20 +4712,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>288</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9767.7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1811985</t>
+          <t>1813565</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -4766,12 +4782,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6665.2</t>
+          <t>6532.2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>763552</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -4819,28 +4835,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>275</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7773.9</t>
+          <t>7539.4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1810383</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>1737053</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4894,12 +4914,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7965.6</t>
+          <t>7311.8</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>95553</t>
+          <t>43785</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4952,23 +4972,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>368</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12058.3</t>
+          <t>11748.6</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1811899</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>456647</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5009,28 +5033,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>387</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12299.6</t>
+          <t>11334.5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1811772</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>56059</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5076,23 +5104,27 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>337</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14223.6</t>
+          <t>12919.4</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1811847</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>120385</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5146,12 +5178,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14038.6</t>
+          <t>12144.9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>421319</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5204,25 +5236,27 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>492</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18630.5</t>
+          <t>18618.6</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1812122</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>85033</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5276,12 +5310,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15299.5</t>
+          <t>13844.9</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>284706</t>
+          <t>99096</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -5329,28 +5363,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>450</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1811964</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>184549</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5367,72 +5405,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5477,25 +5515,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -5556,12 +5594,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>59</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5622,12 +5660,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -5688,12 +5726,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -5754,12 +5792,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -5820,12 +5858,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -5886,12 +5924,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5952,12 +5990,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -6018,12 +6056,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>196.2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>69926</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -6071,32 +6109,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>275.3</t>
+          <t>460.9</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1806819</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6137,25 +6171,25 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>408.7</t>
+          <t>400.8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -6216,12 +6250,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>310.1</t>
+          <t>432.9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -6274,20 +6308,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9687.6</t>
+          <t>9496.1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1813421</t>
+          <t>1812365</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -6336,20 +6370,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9767.7</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1813565</t>
+          <t>1811985</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -6406,12 +6440,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6532.2</t>
+          <t>6665.2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>763552</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -6459,32 +6493,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7539.4</t>
+          <t>7773.9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1737053</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1810383</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6538,12 +6568,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7311.8</t>
+          <t>7965.6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43785</t>
+          <t>95553</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -6596,27 +6626,23 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>376</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11748.6</t>
+          <t>12058.3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>456647</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811899</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6657,32 +6683,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>403</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11334.5</t>
+          <t>12299.6</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>56059</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811772</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6728,27 +6750,23 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>345</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12919.4</t>
+          <t>14223.6</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>120385</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811847</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6802,12 +6820,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>12144.9</t>
+          <t>14038.6</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>58375</t>
+          <t>421319</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -6860,27 +6878,25 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>492</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18618.6</t>
+          <t>18630.5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85033</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812122</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6934,12 +6950,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>13844.9</t>
+          <t>15299.5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>284706</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -6987,32 +7003,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>456</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>184549</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811964</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7029,72 +7041,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -8687,72 +8699,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -10345,72 +10357,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
